--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_los_lagos.xlsx
@@ -375,451 +375,451 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C2">
-        <v>211421</v>
+        <v>94.0611138491868</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C3">
-        <v>142125</v>
+        <v>93.56123464985065</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="C4">
-        <v>42045</v>
+        <v>92.23246039443906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="C5">
-        <v>38911</v>
+        <v>92.0935703084161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C6">
-        <v>35752</v>
+        <v>91.90696695432541</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C7">
-        <v>33828</v>
+        <v>91.63981382026495</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="C8">
-        <v>26473</v>
+        <v>91.60365647218147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="C9">
-        <v>18566</v>
+        <v>91.07537688442211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C10">
-        <v>17589</v>
+        <v>91.00822009729912</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C11">
-        <v>16234</v>
+        <v>90.59394499653339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C12">
-        <v>15851</v>
+        <v>90.46643913538111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="C13">
-        <v>14094</v>
+        <v>90.26643329443796</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="C14">
-        <v>13760</v>
+        <v>90.0110987791343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="C15">
-        <v>13593</v>
+        <v>89.67556909840474</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C16">
-        <v>13591</v>
+        <v>89.30908845556979</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C17">
-        <v>11411</v>
+        <v>89.23476005188067</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C18">
-        <v>10850</v>
+        <v>89.08730158730158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="C19">
-        <v>10006</v>
+        <v>88.3523416646445</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C20">
-        <v>8733</v>
+        <v>88.34567901234568</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="C21">
-        <v>7952</v>
+        <v>87.8411630584464</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C22">
-        <v>7840</v>
+        <v>86.9643315370798</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C23">
-        <v>7634</v>
+        <v>86.74060382008626</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C24">
-        <v>7039</v>
+        <v>85.99251342700592</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="C25">
-        <v>5119</v>
+        <v>85.81255793530761</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="C26">
-        <v>4041</v>
+        <v>85.75845532559313</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C27">
-        <v>3641</v>
+        <v>85.57540725170783</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C28">
-        <v>3389</v>
+        <v>82.94039379544579</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C29">
-        <v>3257</v>
+        <v>81.02561137769555</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C30">
-        <v>2433</v>
+        <v>80.42552058369282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C31">
-        <v>1789</v>
+        <v>68.75252398992328</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
